--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-06-2025.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4025-2400x1200x25mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4030-2400x1200x30mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4050-2400x1200x50mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
